--- a/pensum/ol12/OL12_Interne_rammebetingelser_Oppgaver_v6.xlsx
+++ b/pensum/ol12/OL12_Interne_rammebetingelser_Oppgaver_v6.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="163">
   <si>
     <t xml:space="preserve">Organisasjonens interne rammebetingelser: oppgaver til kapittel 12</t>
   </si>
@@ -65,10 +65,19 @@
     <t xml:space="preserve">Dette er øvingsmateriell til repetisjons- og øvingsstøtte. I besvarelser, caser, prosjektoppgaver og eksamen gjelder lærebøkene og oppgitte primærkilder.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formell kompetanse</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1A: Nordlys: kompetansen, timelistene og hjørnene som må flytte seg</t>
   </si>
   <si>
+    <t xml:space="preserve">Realkompetanse</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alene, i par eller i gruppe, slik du vil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personlig egenskap</t>
   </si>
   <si>
     <t xml:space="preserve">Situasjonen</t>
@@ -116,24 +125,45 @@
     <t xml:space="preserve">a) Sorter kompetansen (velg i nedtrekksmenyen)</t>
   </si>
   <si>
+    <t xml:space="preserve">Mål</t>
+  </si>
+  <si>
     <t xml:space="preserve">Toms fagbrev</t>
   </si>
   <si>
+    <t xml:space="preserve">Deltagere</t>
+  </si>
+  <si>
     <t xml:space="preserve">Toms kursbevis i internkontroll</t>
   </si>
   <si>
+    <t xml:space="preserve">Teknologi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Toms tjue år med feilsøking</t>
   </si>
   <si>
+    <t xml:space="preserve">Sosial struktur</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ronnys tolv år som leder på bygg</t>
   </si>
   <si>
+    <t xml:space="preserve">Riktig: lang erfaring teller som formell kompetanse</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ronny er direkte og god med lærlinger</t>
   </si>
   <si>
+    <t xml:space="preserve">Feil: erfaringen er realkompetanse og kompetansen skal utvikles hele tiden</t>
+  </si>
+  <si>
     <t xml:space="preserve">Saras vitnemål fra Vg2</t>
   </si>
   <si>
+    <t xml:space="preserve">Riktig: kursbevis er bare papir og betyr lite</t>
+  </si>
+  <si>
     <t xml:space="preserve">b) Timelistene skrives for hånd og tastes inn på nytt. Hvilket hjørne i Leavitts diamant hører problemet først og fremst til?</t>
   </si>
   <si>
@@ -155,7 +185,16 @@
     <t xml:space="preserve">Gule celler fyller du inn. Grønne regnes ut av arket. Sjekken til høyre forteller om svaret stemmer, og hva du bør se på hvis ikke.</t>
   </si>
   <si>
+    <t xml:space="preserve">Produksjonsteknologi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1B: Fjell Elektro: teknologien, timene som ikke bidrar, og et verktøy med kunstig intelligens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administrativ teknologi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ikke teknologi</t>
   </si>
   <si>
     <t xml:space="preserve">Fjell Elektro AS i Oslo har vært i drift i ett år. Mona Fjell er eier, daglig leder og faglig ansvarlig, og skriver alle tilbudene selv. Montørene henter materiell på grossistens hentelager fire ganger i uka, 45 minutter per tur. Mona vurderer et verktøy med kunstig intelligens som lager utkast til tilbudstekst og dokumentasjon for forvaltning, drift og vedlikehold, for 400 kr i måneden. Hun sier: «Vi er tre elektrikere. Teknologi har vi nesten ikke.»</t>
@@ -194,12 +233,21 @@
     <t xml:space="preserve">Isolasjonsmåleren</t>
   </si>
   <si>
+    <t xml:space="preserve">Riktig: teknologi er datamaskiner og automatisering</t>
+  </si>
+  <si>
     <t xml:space="preserve">De to servicebilene</t>
   </si>
   <si>
+    <t xml:space="preserve">Feil: teknologi er verktøy og metoder i produksjonen og rutinene som støtter den</t>
+  </si>
+  <si>
     <t xml:space="preserve">Montørenes kunnskap om gjeldende norm</t>
   </si>
   <si>
+    <t xml:space="preserve">Riktig: små bedrifter har ingen teknologi før de kjøper programvare</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fakturarutinen</t>
   </si>
   <si>
@@ -236,9 +284,15 @@
     <t xml:space="preserve">g) Bør Mona ta i bruk verktøyet med kunstig intelligens? Bruk bokas tre spørsmål om teknologi (kvalitet, kostnad, trygghet), og si hvor grensen går for hva verktøyet kan gjøre. To til tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formelt trekk</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1C: Nordlys: strukturen i permen og utenfor, og hvorfor banken sa nei</t>
   </si>
   <si>
+    <t xml:space="preserve">Uformelt trekk</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nordlys har 18 ansatte i tre avdelinger. Bedriften har organisasjonskart og arbeidsavtaler, men ingen stillingsinstrukser. Solcelle og lading har to montører og ingen leder; de løser alt selv. Tom setter prisen selv på service og spør Kari først når jobben passerer et døgnverk, men det står ikke skrevet noe sted. Et borettslag med 90 leiligheter vil ha et ladeanlegg: kontraktsum 3 400 000 kr, dekningsgrad 42 %, 1 450 montørtimer. Materiellet, 35 % av kontrakten, må kjøpes før borettslaget betaler. Banken har sagt nei til å finansiere det.</t>
   </si>
   <si>
@@ -267,6 +321,15 @@
   </si>
   <si>
     <t xml:space="preserve">Dekningsgrad, prosent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organisasjonskultur: normene hele bedriften deler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subkultur: normer som deles av et mindretall og som kan bære eller skade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Et formelt trekk: arbeidsdelingen i avdelingen</t>
   </si>
   <si>
     <t xml:space="preserve">1. Sorter åtte trekk ved Nordlys i formelle og uformelle (a). Formelle trekk er nedskrevne og vedtatte og kan leses ut av bedriftens egne dokumenter. Uformelle trekk står ingen steder.
@@ -645,7 +708,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -668,6 +731,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1114,7 +1181,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G41"/>
+  <dimension ref="B1:Z41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1122,314 +1189,398 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z13" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+      <c r="Z14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z15" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>14</v>
-      </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="B16" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="Z16" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
+      <c r="B17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="Z17" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z18" s="0" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
+      <c r="B19" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="Z19" s="6" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="15"/>
-      <c r="G20" s="16" t="str">
+      <c r="B20" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="G20" s="17" t="str">
         <f aca="false">IF(C20="","Velg i nedtrekksmenyen.",IF(C20="Formell kompetanse","Riktig. Fagbrevet er et dokument, på linje med vitnemål og sertifikater (12.2).","Ikke riktig. Fagbrevet er et dokument, på linje med vitnemål og sertifikater (12.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z20" s="6" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="15"/>
-      <c r="G21" s="16" t="str">
+      <c r="B21" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="G21" s="17" t="str">
         <f aca="false">IF(C21="","Velg i nedtrekksmenyen.",IF(C21="Formell kompetanse","Riktig. Kursbevis står i bokas liste over det som dokumenterer kompetanse (12.2).","Ikke riktig. Kursbevis står i bokas liste over det som dokumenterer kompetanse (12.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z21" s="6" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="15"/>
-      <c r="G22" s="16" t="str">
+      <c r="B22" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="G22" s="17" t="str">
         <f aca="false">IF(C22="","Velg i nedtrekksmenyen.",IF(C22="Realkompetanse","Riktig. Det han faktisk kan, uten papir på det (12.2).","Ikke riktig. Det han faktisk kan, uten papir på det (12.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z22" s="6" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="G23" s="16" t="str">
+      <c r="B23" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="G23" s="17" t="str">
         <f aca="false">IF(C23="","Velg i nedtrekksmenyen.",IF(C23="Realkompetanse","Riktig. Erfaring uten dokumentert lederopplæring er realkompetanse (12.2).","Ikke riktig. Erfaring uten dokumentert lederopplæring er realkompetanse (12.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z23" s="6" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="15"/>
-      <c r="G24" s="16" t="str">
+      <c r="B24" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="G24" s="17" t="str">
         <f aca="false">IF(C24="","Velg i nedtrekksmenyen.",IF(C24="Personlig egenskap","Riktig. En måte å være på, som samarbeidsevne og empati i bokas liste (12.2).","Ikke riktig. En måte å være på, som samarbeidsevne og empati i bokas liste (12.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z24" s="6" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="G25" s="16" t="str">
+      <c r="B25" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="G25" s="17" t="str">
         <f aca="false">IF(C25="","Velg i nedtrekksmenyen.",IF(C25="Formell kompetanse","Riktig. Vitnemål er bokas første eksempel på formell kompetanse (12.2).","Ikke riktig. Vitnemål er bokas første eksempel på formell kompetanse (12.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z25" s="6" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="15"/>
-      <c r="G27" s="16" t="str">
+      <c r="B27" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="G27" s="17" t="str">
         <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Teknologi","Riktig. Teknologi er verktøy og metoder i produksjonen, og også de administrative rutinene som støtter den. Tabell 12.1 fører registrering av tidsforbruk under administrativ teknologi (12.3).","Ikke riktig. Teknologi er verktøy og metoder i produksjonen, og også de administrative rutinene som støtter den. Tabell 12.1 fører registrering av tidsforbruk under administrativ teknologi (12.3)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="G29" s="16" t="str">
+      <c r="B29" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29" s="17" t="str">
         <f aca="false">IF(C29="","Skriv svaret i den gule cellen.",IF(C29=(C12*C13),"Riktig.",IF(ABS(C29-(C12*52))&lt;=0,"Du har ganget med 52 uker. Nordlys har 46 arbeidsuker; ferie og helligdager er trukket fra.",IF(ABS(C29-(C12))&lt;=0,"Det er timene per uke. Gang med antall arbeidsuker for å få timene i året.",IF(ABS(C29-(C12*C13*2))&lt;=0,"Du har doblet. De 6 timene er allerede tiden til den andre inntastingen.","Ikke riktig ennå. Timer i året er timer per uke ganger antall arbeidsuker.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="15"/>
-      <c r="G31" s="16" t="str">
+      <c r="B31" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="16"/>
+      <c r="G31" s="17" t="str">
         <f aca="false">IF(C31="","Velg i nedtrekksmenyen.",IF(C31="Feil: erfaringen er realkompetanse og kompetansen skal utvikles hele tiden","Riktig. Erfaringen er realkompetanse. Kursbeviset fra 2015 dokumenterer kunnskap om normen slik den var da. Boka sier at utdanning, erfaring og de andre egenskapene ikke er konstante, men kan og bør utvikles kontinuerlig (12.2).","Ikke riktig. Erfaringen er realkompetanse. Kursbeviset fra 2015 dokumenterer kunnskap om normen slik den var da. Boka sier at utdanning, erfaring og de andre egenskapene ikke er konstante, men kan og bør utvikles kontinuerlig (12.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
+      <c r="B33" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="20" t="str">
+      <c r="B37" s="21" t="str">
         <f aca="false">IF(LEN(B34)&lt;40,"",IF(AND(ISNUMBER(SEARCH("lær",B34)),ISNUMBER(SEARCH("mål",B34))),"Bra: du har med at folkene må lære verktøyet, og at de frigjorte timene må brukes til noe som bidrar til målet. Si også hvem på kontoret som skal eie den nye rutinen (sosial struktur).",IF(OR(ISNUMBER(SEARCH("lær",B34)),ISNUMBER(SEARCH("mål",B34))),"Du er på sporet. Gå rundt diamanten: deltagerne må læres opp, noen må eie rutinen (sosial struktur), og de 276 timene må brukes til noe som bidrar til målet.","Tips: start i teknologihjørnet og gå til de tre andre. Deltagere: 14 montører og lærlinger må lære verktøyet, og Tom og Ronny må følge opp. Sosial struktur: den som tastet inn, får nye oppgaver, og noen må eie rutinen. Mål: 276 timer er bare en gevinst hvis de brukes til noe som bidrar.")))</f>
         <v/>
       </c>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" s="15"/>
+      <c r="B38" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="16"/>
     </row>
     <row r="39" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="22" t="str">
+      <c r="B39" s="23" t="str">
         <f aca="false">IF(C38="JA","Hint: a: spør om det finnes et papir. Fagbrev, kursbevis og vitnemål er formell kompetanse; erfaring er realkompetanse; hvordan en person er, er en personlig egenskap. b: timelister er en administrativ rutine, altså teknologi. c: 6 × 46 = 276 timer. d: erfaring er realkompetanse, og kompetansen skal utvikles. e: deltagere må læres opp, noen må eie rutinen, og timene må brukes til noe som bidrar til målet.","")</f>
         <v/>
       </c>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
+      <c r="B41" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1524,35 +1675,35 @@
   </conditionalFormatting>
   <dataValidations count="9">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C20" type="list">
-      <formula1>"Formell kompetanse,Realkompetanse,Personlig egenskap"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C21" type="list">
-      <formula1>"Formell kompetanse,Realkompetanse,Personlig egenskap"</formula1>
+      <formula1>$Z$4:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C22" type="list">
-      <formula1>"Formell kompetanse,Realkompetanse,Personlig egenskap"</formula1>
+      <formula1>$Z$7:$Z$9</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C23" type="list">
-      <formula1>"Formell kompetanse,Realkompetanse,Personlig egenskap"</formula1>
+      <formula1>$Z$10:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C24" type="list">
-      <formula1>"Formell kompetanse,Realkompetanse,Personlig egenskap"</formula1>
+      <formula1>$Z$13:$Z$15</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"Formell kompetanse,Realkompetanse,Personlig egenskap"</formula1>
+      <formula1>$Z$16:$Z$18</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Mål,Deltagere,Teknologi,Sosial struktur"</formula1>
+      <formula1>$Z$19:$Z$22</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C31" type="list">
-      <formula1>"Riktig: lang erfaring teller som formell kompetanse,Feil: erfaringen er realkompetanse og kompetansen skal utvikles hele tiden,Riktig: kursbevis er bare papir og betyr lite"</formula1>
+      <formula1>$Z$23:$Z$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C38" type="list">
@@ -1575,7 +1726,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G46"/>
+  <dimension ref="B1:Z46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1583,369 +1734,450 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>52</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>45</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
+      <c r="Z13" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>46</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>46</v>
+      <c r="Z14" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="12" t="n">
+      <c r="B15" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="13" t="n">
         <v>890</v>
       </c>
+      <c r="Z15" s="6" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="12" t="n">
+      <c r="B16" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="13" t="n">
         <v>400</v>
       </c>
+      <c r="Z16" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z17" s="0" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="B18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="Z18" s="6" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="B19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="Z19" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z20" s="0" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
+      <c r="B21" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="Z21" s="6" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="15"/>
-      <c r="G22" s="16" t="str">
+      <c r="B22" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="G22" s="17" t="str">
         <f aca="false">IF(C22="","Velg i nedtrekksmenyen.",IF(C22="Produksjonsteknologi","Riktig. Verktøy i produksjonen (12.3).","Ikke riktig. Verktøy i produksjonen (12.3)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z22" s="6" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="G23" s="16" t="str">
+      <c r="B23" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="G23" s="17" t="str">
         <f aca="false">IF(C23="","Velg i nedtrekksmenyen.",IF(C23="Produksjonsteknologi","Riktig. Bilene er verktøy i produksjonen, som godsbilene hos transportbyrået i tabell 12.1.","Ikke riktig. Bilene er verktøy i produksjonen, som godsbilene hos transportbyrået i tabell 12.1."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z23" s="6" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="15"/>
-      <c r="G24" s="16" t="str">
+      <c r="B24" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="G24" s="17" t="str">
         <f aca="false">IF(C24="","Velg i nedtrekksmenyen.",IF(C24="Produksjonsteknologi","Riktig. Tabell 12.1 fører fagfolk med godkjent kompetanse under produksjonsteknologi. Her henger teknologihjørnet sammen med deltagerhjørnet.","Ikke riktig. Tabell 12.1 fører fagfolk med godkjent kompetanse under produksjonsteknologi. Her henger teknologihjørnet sammen med deltagerhjørnet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z24" s="6" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="G25" s="16" t="str">
+      <c r="B25" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="G25" s="17" t="str">
         <f aca="false">IF(C25="","Velg i nedtrekksmenyen.",IF(C25="Administrativ teknologi","Riktig. Fakturering står under administrativ teknologi i tabell 12.1.","Ikke riktig. Fakturering står under administrativ teknologi i tabell 12.1."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="15"/>
-      <c r="G26" s="16" t="str">
+      <c r="B26" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="G26" s="17" t="str">
         <f aca="false">IF(C26="","Velg i nedtrekksmenyen.",IF(C26="Administrativ teknologi","Riktig. Registrering av tidsforbruk er administrativ teknologi (tabell 12.1).","Ikke riktig. Registrering av tidsforbruk er administrativ teknologi (tabell 12.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="15"/>
-      <c r="G27" s="16" t="str">
+      <c r="B27" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="G27" s="17" t="str">
         <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Administrativ teknologi","Riktig. Det støtter produksjonen uten å være en del av den. Boka kaller slik teknologi nødvendig, men ikke direkte inntektsgivende (12.3).","Ikke riktig. Det støtter produksjonen uten å være en del av den. Boka kaller slik teknologi nødvendig, men ikke direkte inntektsgivende (12.3)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="15"/>
-      <c r="G28" s="16" t="str">
+      <c r="B28" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="G28" s="17" t="str">
         <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Ikke teknologi","Riktig. Renten settes utenfor bedriften. Det er en ekstern ramme (kapittel 13), ikke teknologi.","Ikke riktig. Renten settes utenfor bedriften. Det er en ekstern ramme (kapittel 13), ikke teknologi."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="G30" s="16" t="str">
+      <c r="B30" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G30" s="17" t="str">
         <f aca="false">IF(C30="","Skriv svaret i den gule cellen.",IF(C30=(C12*C13/60*C14),"Riktig.",IF(ABS(C30-(C12*C13/100*C14))&lt;=0,"Du har regnet 45 minutter som 0,45 time. Minutter deles på 60: 45 / 60 = 0,75 time.",IF(ABS(C30-(C12*C13/60*52))&lt;=0,"Du har ganget med 52 uker. Fjell har 46 arbeidsuker.",IF(ABS(C30-(C12*C13*C14))&lt;=0,"Du har svart i minutter. Del på 60 for å få timer.","Ikke riktig ennå. Turer per uke × timer per tur × arbeidsuker. 45 minutter er 0,75 time.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G31" s="16" t="str">
+      <c r="B31" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="18"/>
+      <c r="D31" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="G31" s="17" t="str">
         <f aca="false">IF(C31="","Skriv svaret i den gule cellen.",IF(C31=(ROUND(C12*C13/60*C14*C15,0)),"Riktig.",IF(ABS(C31-(ROUND(C12*C13/60*C14*C15*1.25,0)))&lt;=0,"Du har lagt på merverdiavgift. Timeprisen 890 kr er uten merverdiavgift, og det er den Fjell sitter igjen med.",IF(ABS(C31-(ROUND(C12*C13/100*C14*C15,0)))&lt;=0,"Timetallet er feil: 45 minutter er 0,75 time, ikke 0,45.","Ikke riktig ennå. Timene fra b ganger 890 kr."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G33" s="16" t="str">
+      <c r="B33" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="18"/>
+      <c r="D33" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="G33" s="17" t="str">
         <f aca="false">IF(C33="","Skriv svaret i den gule cellen.",IF(C33=(C16*12),"Riktig.",IF(ABS(C33-(C16))&lt;=0,"Det er prisen per måned. Gang med 12.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G34" s="16" t="str">
+      <c r="B34" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="24"/>
+      <c r="D34" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34" s="17" t="str">
         <f aca="false">IF(C34="","Skriv svaret i den gule cellen.",IF(ABS(C34-(ROUND(C16*12/C15,1)))&lt;=0.05,"Riktig.",IF(ABS(C34-(ROUND(C16/C15,1)))&lt;=0.05,"Du har delt månedsprisen på timeprisen. Bruk årskostnaden fra d.",IF(ABS(C34-(ROUND(C15/(C16*12),1)))&lt;=0.05,"Du har delt motsatt vei. Det er kostnaden som skal deles på timeprisen.","Ikke riktig ennå. Årskostnaden fra d delt på timeprisen 890 kr."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" s="15"/>
-      <c r="G36" s="16" t="str">
+      <c r="B36" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" s="16"/>
+      <c r="G36" s="17" t="str">
         <f aca="false">IF(C36="","Velg i nedtrekksmenyen.",IF(C36="Feil: teknologi er verktøy og metoder i produksjonen og rutinene som støtter den","Riktig. Boka definerer teknologi som verktøyet og metodene organisasjonen bruker i produksjonsprosessen, og tar med administrative verktøy og rutiner (12.3). Tabell 12.1 fører opp hammer, sag og stiger for tømrerfirmaet. Fjells verktøy, biler, måleinstrumenter og fakturarutiner er teknologi.","Ikke riktig. Boka definerer teknologi som verktøyet og metodene organisasjonen bruker i produksjonsprosessen, og tar med administrative verktøy og rutiner (12.3). Tabell 12.1 fører opp hammer, sag og stiger for tømrerfirmaet. Fjells verktøy, biler, måleinstrumenter og fakturarutiner er teknologi."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
+      <c r="B38" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
     </row>
     <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="20" t="str">
+      <c r="B42" s="21" t="str">
         <f aca="false">IF(LEN(B39)&lt;40,"",IF(AND(ISNUMBER(SEARCH("kvalitet",B39)),ISNUMBER(SEARCH("ansvar",B39))),"Bra: du vurderer kvaliteten på utkastet og sier hvor ansvaret ligger. Prisen er ikke problemet; 5,4 fakturerbare timer i året betaler verktøyet.",IF(OR(ISNUMBER(SEARCH("kvalitet",B39)),ISNUMBER(SEARCH("ansvar",B39))),"Du har med noe av det. Svar på alle tre: er kvaliteten god nok uten at en fagperson leser, er 4 800 kr i året verdt det, og hvem har ansvaret for det som sendes ut?","Tips: kvalitet: utkastet ser faglig ut, men må leses og rettes av Mona. Kostnad: 4 800 kr i året er 5,4 fakturerbare timer; verktøyet betaler seg hvis det frigjør mer. Trygghet: Mona er faglig ansvarlig og signerer; ansvaret kan ikke settes ut til et verktøy.")))</f>
         <v/>
       </c>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C43" s="15"/>
+      <c r="B43" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="16"/>
     </row>
     <row r="44" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="22" t="str">
+      <c r="B44" s="23" t="str">
         <f aca="false">IF(C43="JA","Hint: a: verktøy, biler og fagkunnskap er produksjonsteknologi; faktura, timer og tilbudsverktøy er administrativ teknologi; renten er ikke teknologi. b: 4 × 0,75 × 46 = 138 timer. c: 138 × 890 = 122 820 kr. d: 400 × 12 = 4 800 kr. e: 4 800 / 890 = 5,4 timer. f: teknologi er også rutinene. g: kvalitet, kostnad, trygghet, og Mona svarer for innholdet.","")</f>
         <v/>
       </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
+      <c r="B46" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2064,35 +2296,35 @@
   </conditionalFormatting>
   <dataValidations count="9">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C22" type="list">
-      <formula1>"Produksjonsteknologi,Administrativ teknologi,Ikke teknologi"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C23" type="list">
-      <formula1>"Produksjonsteknologi,Administrativ teknologi,Ikke teknologi"</formula1>
+      <formula1>$Z$4:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C24" type="list">
-      <formula1>"Produksjonsteknologi,Administrativ teknologi,Ikke teknologi"</formula1>
+      <formula1>$Z$7:$Z$9</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"Produksjonsteknologi,Administrativ teknologi,Ikke teknologi"</formula1>
+      <formula1>$Z$10:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C26" type="list">
-      <formula1>"Produksjonsteknologi,Administrativ teknologi,Ikke teknologi"</formula1>
+      <formula1>$Z$13:$Z$15</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Produksjonsteknologi,Administrativ teknologi,Ikke teknologi"</formula1>
+      <formula1>$Z$16:$Z$18</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Produksjonsteknologi,Administrativ teknologi,Ikke teknologi"</formula1>
+      <formula1>$Z$19:$Z$21</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C36" type="list">
-      <formula1>"Riktig: teknologi er datamaskiner og automatisering,Feil: teknologi er verktøy og metoder i produksjonen og rutinene som støtter den,Riktig: små bedrifter har ingen teknologi før de kjøper programvare"</formula1>
+      <formula1>$Z$22:$Z$24</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C43" type="list">
@@ -2115,7 +2347,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G48"/>
+  <dimension ref="B1:Z48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2123,401 +2355,465 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>84</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>72</v>
+      <c r="B11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>2892650</v>
       </c>
+      <c r="Z12" s="6" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>7290000</v>
       </c>
+      <c r="Z13" s="6" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="24" t="n">
+      <c r="B14" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="25" t="n">
         <f aca="false">C12+C13</f>
         <v>10182650</v>
       </c>
+      <c r="Z14" s="6" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="12" t="n">
+      <c r="B15" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="13" t="n">
         <v>3400000</v>
       </c>
+      <c r="Z15" s="6" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="12" t="n">
+      <c r="B16" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="13" t="n">
         <v>35</v>
       </c>
+      <c r="Z16" s="6" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="12" t="n">
+      <c r="B17" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="13" t="n">
         <v>42</v>
       </c>
+      <c r="Z17" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z18" s="0" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
+      <c r="B19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="Z19" s="6" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+      <c r="B20" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
+      <c r="B22" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="G23" s="16" t="str">
+      <c r="B23" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="G23" s="17" t="str">
         <f aca="false">IF(C23="","Velg i nedtrekksmenyen.",IF(C23="Formelt trekk","Riktig. Nedskrevet og vedtatt; står i bokas liste over formelle trekk (12.4).","Ikke riktig. Nedskrevet og vedtatt; står i bokas liste over formelle trekk (12.4)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="15"/>
-      <c r="G24" s="16" t="str">
+      <c r="B24" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="G24" s="17" t="str">
         <f aca="false">IF(C24="","Velg i nedtrekksmenyen.",IF(C24="Formelt trekk","Riktig. Et dokument som kan leses: formelt (12.4).","Ikke riktig. Et dokument som kan leses: formelt (12.4)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="G25" s="16" t="str">
+      <c r="B25" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="G25" s="17" t="str">
         <f aca="false">IF(C25="","Velg i nedtrekksmenyen.",IF(C25="Formelt trekk","Riktig. Rutiner og prosedyrer er formelle trekk (12.4).","Ikke riktig. Rutiner og prosedyrer er formelle trekk (12.4)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" s="15"/>
-      <c r="G26" s="16" t="str">
+      <c r="B26" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="G26" s="17" t="str">
         <f aca="false">IF(C26="","Velg i nedtrekksmenyen.",IF(C26="Uformelt trekk","Riktig. Horisontal kommunikasjon, altså på tvers, står i bokas liste over uformelle trekk (12.4).","Ikke riktig. Horisontal kommunikasjon, altså på tvers, står i bokas liste over uformelle trekk (12.4)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" s="15"/>
-      <c r="G27" s="16" t="str">
+      <c r="B27" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="G27" s="17" t="str">
         <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Uformelt trekk","Riktig. Tillitsforholdet mellom over- og underordnede er et uformelt trekk (12.4).","Ikke riktig. Tillitsforholdet mellom over- og underordnede er et uformelt trekk (12.4)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" s="15"/>
-      <c r="G28" s="16" t="str">
+      <c r="B28" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="G28" s="17" t="str">
         <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Uformelt trekk","Riktig. Det psykososiale arbeidsmiljøet er et uformelt trekk (12.4).","Ikke riktig. Det psykososiale arbeidsmiljøet er et uformelt trekk (12.4)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" s="15"/>
-      <c r="G29" s="16" t="str">
+      <c r="B29" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="16"/>
+      <c r="G29" s="17" t="str">
         <f aca="false">IF(C29="","Velg i nedtrekksmenyen.",IF(C29="Uformelt trekk","Riktig. En norm som ikke står noe sted; en subkultur (12.4).","Ikke riktig. En norm som ikke står noe sted; en subkultur (12.4)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" s="15"/>
-      <c r="G30" s="16" t="str">
+      <c r="B30" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" s="16"/>
+      <c r="G30" s="17" t="str">
         <f aca="false">IF(C30="","Velg i nedtrekksmenyen.",IF(C30="Uformelt trekk","Riktig. Grensen finnes bare muntlig. Skrives den ned som en fullmaktsgrense, blir den et formelt trekk.","Ikke riktig. Grensen finnes bare muntlig. Skrives den ned som en fullmaktsgrense, blir den et formelt trekk."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32" s="15"/>
-      <c r="G32" s="16" t="str">
+      <c r="B32" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="16"/>
+      <c r="G32" s="17" t="str">
         <f aca="false">IF(C32="","Velg i nedtrekksmenyen.",IF(C32="Subkultur: normer som deles av et mindretall og som kan bære eller skade","Riktig. En subkultur er normer og verdier som deles av et mindretall og framstår som avvikende. Boka sier at subkulturer kan være ødeleggende, men også bidra positivt (12.4). Her bærer den avdelingen og skjuler at den mangler leder.","Ikke riktig. En subkultur er normer og verdier som deles av et mindretall og framstår som avvikende. Boka sier at subkulturer kan være ødeleggende, men også bidra positivt (12.4). Her bærer den avdelingen og skjuler at den mangler leder."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G34" s="16" t="str">
+      <c r="B34" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" s="24"/>
+      <c r="D34" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="G34" s="17" t="str">
         <f aca="false">IF(C34="","Skriv svaret i den gule cellen.",IF(ABS(C34-(ROUND(C12/C14*100,1)))&lt;=0.05,"Riktig.",IF(ABS(C34-(ROUND(C12/C13*100,1)))&lt;=0.05,"Du har delt på gjelden. Egenkapitalandelen er egenkapital delt på totalkapitalen (egenkapital pluss gjeld).",IF(ABS(C34-(ROUND(C13/C14*100,1)))&lt;=0.05,"Det er gjeldens andel. Egenkapitalandelen er egenkapitalen delt på totalkapitalen.","Ikke riktig ennå. Egenkapital delt på totalkapital, ganger 100."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="C35" s="23"/>
-      <c r="D35" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G35" s="16" t="str">
+      <c r="B35" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="24"/>
+      <c r="D35" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="G35" s="17" t="str">
         <f aca="false">IF(C35="","Skriv svaret i den gule cellen.",IF(ABS(C35-(ROUND(C13/C14*100,1)))&lt;=0.05,"Riktig.",IF(ABS(C35-(ROUND(C13/C12*100,1)))&lt;=0.05,"Du har delt gjelden på egenkapitalen. Det er gjeldsgraden slik Økonomistyring regner den. Boka her mener gjeld delt på totalkapitalen.","Ikke riktig ennå. Gjeld delt på totalkapital, ganger 100. Eller 100 minus egenkapitalandelen.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G36" s="16" t="str">
+      <c r="B36" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="G36" s="17" t="str">
         <f aca="false">IF(C36="","Skriv svaret i den gule cellen.",IF(C36=(C15*C16/100),"Riktig.",IF(ABS(C36-(C15*C17/100))&lt;=0,"Du har regnet dekningsbidraget (42 %). Materiellet er 35 % av kontraktsummen.",IF(ABS(C36-(C15))&lt;=0,"Det er hele kontraktsummen. Materiellet er 35 % av den.","Ikke riktig ennå. 35 % av 3 400 000."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C37" s="23"/>
-      <c r="D37" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G37" s="16" t="str">
+      <c r="B37" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" s="24"/>
+      <c r="D37" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="G37" s="17" t="str">
         <f aca="false">IF(C37="","Skriv svaret i den gule cellen.",IF(ABS(C37-(ROUND(C12/(C14+C15*C16/100)*100,1)))&lt;=0.05,"Riktig.",IF(ABS(C37-(ROUND(C12/C14*100,1)))&lt;=0.05,"Du har glemt at totalkapitalen øker med lånet. Legg 1 190 000 til totalkapitalen før du deler.",IF(ABS(C37-(ROUND((C12-C15*C16/100)/C14*100,1)))&lt;=0.05,"Du har trukket lånet fra egenkapitalen. Et lån øker gjelden og totalkapitalen; egenkapitalen er den samme.","Ikke riktig ennå. 2 892 650 delt på (10 182 650 + 1 190 000), ganger 100."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="C38" s="17"/>
-      <c r="D38" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G38" s="16" t="str">
+      <c r="B38" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="G38" s="17" t="str">
         <f aca="false">IF(C38="","Skriv svaret i den gule cellen.",IF(ABS(C38-(ROUND(C14*0.35-C12,0)))&lt;=1,"Riktig.",IF(ABS(C38-(ROUND(C14*0.35,0)))&lt;=1,"Det er egenkapitalen Nordlys måtte hatt. Trekk fra den egenkapitalen de har, 2 892 650.",IF(ABS(C38-(ROUND((C14+C15*C16/100)*0.35-C12,0)))&lt;=1,"Du har brukt totalkapitalen med lånet. Oppgaven spør om dagens balanse, 10 182 650.","Ikke riktig ennå. 35 % av 10 182 650 minus 2 892 650."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
+      <c r="B40" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
     </row>
     <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="20" t="str">
+      <c r="B44" s="21" t="str">
         <f aca="false">IF(LEN(B41)&lt;40,"",IF(AND(ISNUMBER(SEARCH("leder",B41)),ISNUMBER(SEARCH("egenkapital",B41))),"Bra: du tar både strukturen (en leder for solcelle og lading) og økonomien (egenkapitalen). Si også hva som er alternativet: forskudd fra borettslaget, eller å la mer av overskuddet bli stående.",IF(OR(ISNUMBER(SEARCH("leder",B41)),ISNUMBER(SEARCH("egenkapital",B41))),"Du har med ett av de to. Ta med det andre også: avdelingen trenger en leder som kan være prosjektleder, og egenkapitalandelen på 28,4 % er grunnen til at banken sier nei.","Tips: struktur: gi solcelle og lading en leder som kan lede ladejobben, og skriv ned hvem som bestemmer hva. Økonomi: med 71,6 % gjeld er Nordlys allerede over bokas grense på 60–65 %, og med lånt materiell faller egenkapitalandelen til 25,4 %. Be borettslaget om forskudd på materiellet, eller la mer av overskuddet bli stående til egenkapitalen er 671 278 kr høyere.")))</f>
         <v/>
       </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C45" s="15"/>
+      <c r="B45" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="16"/>
     </row>
     <row r="46" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="22" t="str">
+      <c r="B46" s="23" t="str">
         <f aca="false">IF(C45="JA","Hint: a: det som står på papir er formelt; kommunikasjon, tillit, stemning og vaner er uformelt. b: subkultur. c: 2 892 650 / 10 182 650 × 100 = 28,4 %. d: 100 − 28,4 = 71,6 %. e: 35 % av 3 400 000 = 1 190 000 kr. f: 2 892 650 / 11 372 650 × 100 = 25,4 %. g: 35 % av 10 182 650 = 3 563 928, minus 2 892 650 = 671 278 kr.","")</f>
         <v/>
       </c>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="22"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="23"/>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
+      <c r="B48" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2652,39 +2948,39 @@
   </conditionalFormatting>
   <dataValidations count="10">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C23" type="list">
-      <formula1>"Formelt trekk,Uformelt trekk"</formula1>
+      <formula1>$Z$1:$Z$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C24" type="list">
-      <formula1>"Formelt trekk,Uformelt trekk"</formula1>
+      <formula1>$Z$3:$Z$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"Formelt trekk,Uformelt trekk"</formula1>
+      <formula1>$Z$5:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C26" type="list">
-      <formula1>"Formelt trekk,Uformelt trekk"</formula1>
+      <formula1>$Z$7:$Z$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Formelt trekk,Uformelt trekk"</formula1>
+      <formula1>$Z$9:$Z$10</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Formelt trekk,Uformelt trekk"</formula1>
+      <formula1>$Z$11:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Formelt trekk,Uformelt trekk"</formula1>
+      <formula1>$Z$13:$Z$14</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C30" type="list">
-      <formula1>"Formelt trekk,Uformelt trekk"</formula1>
+      <formula1>$Z$15:$Z$16</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
-      <formula1>"Organisasjonskultur: normene hele bedriften deler,Subkultur: normer som deles av et mindretall og som kan bære eller skade,Et formelt trekk: arbeidsdelingen i avdelingen"</formula1>
+      <formula1>$Z$17:$Z$19</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C45" type="list">
@@ -2717,226 +3013,226 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="25" t="s">
-        <v>97</v>
+      <c r="B2" s="26" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>101</v>
+      <c r="B5" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="27" t="s">
-        <v>103</v>
+      <c r="B6" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="25"/>
+      <c r="D6" s="28" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="27" t="s">
-        <v>105</v>
+      <c r="B7" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="28" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="C8" s="24" t="n">
+      <c r="B8" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="25" t="n">
         <v>276</v>
       </c>
-      <c r="D8" s="27" t="s">
-        <v>107</v>
+      <c r="D8" s="28" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="27" t="s">
-        <v>109</v>
+      <c r="B9" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="28" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" s="24"/>
-      <c r="D10" s="27" t="s">
-        <v>111</v>
+      <c r="B10" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="25"/>
+      <c r="D10" s="28" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="27" t="s">
-        <v>113</v>
+      <c r="B11" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11" s="25"/>
+      <c r="D11" s="28" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="24" t="n">
+      <c r="B12" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="25" t="n">
         <v>138</v>
       </c>
-      <c r="D12" s="27" t="s">
-        <v>115</v>
+      <c r="D12" s="28" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="C13" s="24" t="n">
+      <c r="B13" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="25" t="n">
         <v>122820</v>
       </c>
-      <c r="D13" s="27" t="s">
-        <v>117</v>
+      <c r="D13" s="28" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="24" t="n">
+      <c r="B14" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="25" t="n">
         <v>4800</v>
       </c>
-      <c r="D14" s="27" t="s">
-        <v>119</v>
+      <c r="D14" s="28" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="C15" s="24" t="n">
+      <c r="B15" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C15" s="25" t="n">
         <v>5.4</v>
       </c>
-      <c r="D15" s="27" t="s">
-        <v>121</v>
+      <c r="D15" s="28" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="27" t="s">
-        <v>123</v>
+      <c r="B16" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="28" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="27" t="s">
-        <v>125</v>
+      <c r="B17" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="28" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="27" t="s">
-        <v>127</v>
+      <c r="B18" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="28" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="C19" s="24"/>
-      <c r="D19" s="27" t="s">
-        <v>129</v>
+      <c r="B19" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="C19" s="25"/>
+      <c r="D19" s="28" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="C20" s="24" t="n">
+      <c r="B20" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C20" s="25" t="n">
         <v>28.4</v>
       </c>
-      <c r="D20" s="27" t="s">
-        <v>131</v>
+      <c r="D20" s="28" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="C21" s="24" t="n">
+      <c r="B21" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="25" t="n">
         <v>71.6</v>
       </c>
-      <c r="D21" s="27" t="s">
-        <v>133</v>
+      <c r="D21" s="28" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="C22" s="24" t="n">
+      <c r="B22" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="C22" s="25" t="n">
         <v>1190000</v>
       </c>
-      <c r="D22" s="27" t="s">
-        <v>135</v>
+      <c r="D22" s="28" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C23" s="24" t="n">
+      <c r="B23" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C23" s="25" t="n">
         <v>25.4</v>
       </c>
-      <c r="D23" s="27" t="s">
-        <v>137</v>
+      <c r="D23" s="28" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="C24" s="24" t="n">
+      <c r="B24" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" s="25" t="n">
         <v>671278</v>
       </c>
-      <c r="D24" s="27" t="s">
-        <v>139</v>
+      <c r="D24" s="28" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="C25" s="24"/>
-      <c r="D25" s="27" t="s">
-        <v>141</v>
+      <c r="B25" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="C25" s="25"/>
+      <c r="D25" s="28" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ol12/OL12_Interne_rammebetingelser_Oppgaver_v6.xlsx
+++ b/pensum/ol12/OL12_Interne_rammebetingelser_Oppgaver_v6.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Situasjonen</t>
   </si>
   <si>
-    <t xml:space="preserve">Kari Nordlund vil innføre digital timeregistrering på mobil for alle de 12 montørene og 2 lærlingene. I dag skriver montørene timelister for hånd, og kontoret taster dem inn på nytt. Før hun bestemmer seg, går hun gjennom folkene. Tom Berg har fagbrev og kurs i internkontroll, kursbeviset på gjeldende norm er fra 2015, og han har tjue år med feilsøking. Ronny Fjeld har fagbrev, tolv år som leder på bygg, ingen dokumentert lederopplæring, og er direkte og god med lærlinger. Lærlingen Sara Lien har vitnemål fra Vg2 og lærekontrakt.</t>
+    <t xml:space="preserve">Kari Nordlund vil innføre digital timeregistrering på mobil for alle de 12 montørene og 2 lærlingene. I dag skriver montørene timelister for hånd, og kontoret taster dem inn på nytt. Før hun bestemmer seg, går hun gjennom folkene. Tom Berg har fagbrev og kurs i internkontroll, kursbeviset er på NEK 400:2014 og fra 2015 (gjeldende er NEK 400:2026 fra 1. juli 2026), og han har tjue år med feilsøking. Ronny Fjeld har fagbrev, tolv år som leder på bygg, ingen dokumentert lederopplæring, og er direkte og god med lærlinger. Lærlingen Sara Lien har vitnemål fra Vg2 og lærekontrakt.</t>
   </si>
   <si>
     <t xml:space="preserve">Begrepene du trenger</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">Uformelt trekk</t>
   </si>
   <si>
-    <t xml:space="preserve">Nordlys har 18 ansatte i tre avdelinger. Bedriften har organisasjonskart og arbeidsavtaler, men ingen stillingsinstrukser. Solcelle og lading har to montører og ingen leder; de løser alt selv. Tom setter prisen selv på service og spør Kari først når jobben passerer et døgnverk, men det står ikke skrevet noe sted. Et borettslag med 90 leiligheter vil ha et ladeanlegg: kontraktsum 3 400 000 kr, dekningsgrad 42 %, 1 450 montørtimer. Materiellet, 35 % av kontrakten, må kjøpes før borettslaget betaler. Banken har sagt nei til å finansiere det.</t>
+    <t xml:space="preserve">Nordlys har 18 ansatte i tre avdelinger. Bedriften har organisasjonskart og arbeidsavtaler, men ingen stillingsinstrukser. Solcelle og lading har to montører og ingen leder; de løser alt selv. Tom setter prisen selv på service og spør Kari først når jobben passerer et døgnverk, men det står ikke skrevet noe sted. Et borettslag med 90 leiligheter vil ha et ladeanlegg: kontraktsum 1 868 850 kr, dekningsgrad 19,9 %, 765 montørtimer. Materiellet, 90 × 11 000 = 990 000 kr netto, bestilles i starten, mens borettslaget betaler a konto etter fremdrift og resten ved sluttoppgjøret, så i verste fall må Nordlys bære det en periode. Polarlys vil ikke øke kredittgrensen, og borettslaget krever sikkerhetsstillelse etter kontrakten. Banken vil ikke stille garantien når egenkapitalandelen er 28,4 %, og uten garanti får Nordlys ikke kontrakten.</t>
   </si>
   <si>
     <t xml:space="preserve">Sosial struktur har formelle trekk (organisasjonskart, arbeidsdeling, stillingsinstrukser, rutiner) og uformelle trekk (holdninger, kommunikasjon, tillit, konfliktnivå, arbeidsmiljø) (12.4). Organisasjonskultur er normene og verdiene som preger organisasjonen; en subkultur deles av et mindretall. God økonomi gir handlefrihet, og gjelden bør ikke overstige 60–65 % av totalkapitalen (12.5.2). Egenkapitalandel = egenkapital / totalkapital × 100.</t>
@@ -314,13 +314,13 @@
     <t xml:space="preserve">Totalkapital (egenkapital pluss gjeld)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ladejobben: kontraktsum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiellets andel av kontraktsummen, prosent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dekningsgrad, prosent</t>
+    <t xml:space="preserve">Ladeanlegget: antall plasser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiell per plass, netto innkjøp, kr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dekningsbidrag per plass, kr</t>
   </si>
   <si>
     <t xml:space="preserve">Organisasjonskultur: normene hele bedriften deler</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">d) Gjeld i prosent av totalkapitalen, én desimal</t>
   </si>
   <si>
-    <t xml:space="preserve">e) Materiellet som må kjøpes før borettslaget betaler</t>
+    <t xml:space="preserve">e) Materiellet som i verste fall må bæres før akontoene og sluttoppgjøret er betalt (netto innkjøp)</t>
   </si>
   <si>
     <t xml:space="preserve">f) Egenkapitalandel hvis materiellet lånes: totalkapitalen øker med lånet, egenkapitalen står stille. Én desimal</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">1B c) Timene i kroner</t>
   </si>
   <si>
-    <t xml:space="preserve">138 timer × 890 kr = 122 820 kr</t>
+    <t xml:space="preserve">138 timer × 890 kr = 122 820 kr. Det er tapt fakturering når timene ellers kunne vært solgt; står montørene ledige, koster hentingen ikke noe ekstra i lønn</t>
   </si>
   <si>
     <t xml:space="preserve">1B d) Verktøyet per år</t>
@@ -503,13 +503,13 @@
     <t xml:space="preserve">1C e) Materiellet som må forskutteres</t>
   </si>
   <si>
-    <t xml:space="preserve">35 % av 3 400 000 = 1 190 000 kr</t>
+    <t xml:space="preserve">90 plasser × 11 000 kr = 990 000 kr netto</t>
   </si>
   <si>
     <t xml:space="preserve">1C f) Egenkapitalandel med lånt materiell</t>
   </si>
   <si>
-    <t xml:space="preserve">2 892 650 / (10 182 650 + 1 190 000) × 100 = 25,4 %</t>
+    <t xml:space="preserve">2 892 650 / (10 182 650 + 990 000) × 100 = 25,9 %</t>
   </si>
   <si>
     <t xml:space="preserve">1C g) Egenkapital som mangler</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">1C h) Rådet til Kari</t>
   </si>
   <si>
-    <t xml:space="preserve">Struktur: en leder for solcelle og lading, som også kan lede ladejobben; skriv ned hvem som bestemmer hva. Økonomi: Nordlys er over bokas grense allerede; be om forskudd på materiellet eller la mer overskudd bli stående</t>
+    <t xml:space="preserve">Struktur: en leder for solcelle og lading, som også kan lede ladejobben; skriv ned hvem som bestemmer hva. Økonomi: Nordlys er over bokas grense allerede; avtal a konto for materiellet i kontrakten, eller la mer overskudd bli stående</t>
   </si>
 </sst>
 </file>
@@ -2067,7 +2067,7 @@
         <v>78</v>
       </c>
       <c r="G31" s="17" t="str">
-        <f aca="false">IF(C31="","Skriv svaret i den gule cellen.",IF(C31=(ROUND(C12*C13/60*C14*C15,0)),"Riktig.",IF(ABS(C31-(ROUND(C12*C13/60*C14*C15*1.25,0)))&lt;=0,"Du har lagt på merverdiavgift. Timeprisen 890 kr er uten merverdiavgift, og det er den Fjell sitter igjen med.",IF(ABS(C31-(ROUND(C12*C13/100*C14*C15,0)))&lt;=0,"Timetallet er feil: 45 minutter er 0,75 time, ikke 0,45.","Ikke riktig ennå. Timene fra b ganger 890 kr."))))</f>
+        <f aca="false">IF(C31="","Skriv svaret i den gule cellen.",IF(C31=(ROUND(C12*C13/60*C14*C15,0)),"Riktig.",IF(ABS(C31-(ROUND(C12*C13/60*C14*C15*1.25,0)))&lt;=0,"Du har lagt på merverdiavgift. Timeprisen 890 kr er uten merverdiavgift, og det er den Fjell sitter igjen med.",IF(ABS(C31-(ROUND(C12*C13/100*C14*C15,0)))&lt;=0,"Timetallet er feil: 45 minutter er 0,75 time, ikke 0,45.","Ikke riktig ennå. Timene fra b ganger 890 kr. Det er tapet hvis timene ellers kunne vært fakturert."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
         <v>87</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>94</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>3400000</v>
+        <v>90</v>
       </c>
       <c r="Z15" s="6" t="s">
         <v>84</v>
@@ -2533,7 +2533,7 @@
         <v>95</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>35</v>
+        <v>11000</v>
       </c>
       <c r="Z16" s="6" t="s">
         <v>86</v>
@@ -2544,7 +2544,7 @@
         <v>96</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>42</v>
+        <v>4125</v>
       </c>
       <c r="Z17" s="6" t="s">
         <v>97</v>
@@ -2713,7 +2713,7 @@
         <v>78</v>
       </c>
       <c r="G36" s="17" t="str">
-        <f aca="false">IF(C36="","Skriv svaret i den gule cellen.",IF(C36=(C15*C16/100),"Riktig.",IF(ABS(C36-(C15*C17/100))&lt;=0,"Du har regnet dekningsbidraget (42 %). Materiellet er 35 % av kontraktsummen.",IF(ABS(C36-(C15))&lt;=0,"Det er hele kontraktsummen. Materiellet er 35 % av den.","Ikke riktig ennå. 35 % av 3 400 000."))))</f>
+        <f aca="false">IF(C36="","Skriv svaret i den gule cellen.",IF(C36=(C15*C16),"Riktig.",IF(ABS(C36-(C15*C17))&lt;=0,"Du har regnet dekningsbidraget (90 × 4 125). Materiellet er 11 000 kr per plass.",IF(ABS(C36-(C16))&lt;=0,"Det er materiellet for én plass. Gang med 90 plasser.","Ikke riktig ennå. 90 plasser × 11 000 kr netto."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
         <v>112</v>
       </c>
       <c r="G37" s="17" t="str">
-        <f aca="false">IF(C37="","Skriv svaret i den gule cellen.",IF(ABS(C37-(ROUND(C12/(C14+C15*C16/100)*100,1)))&lt;=0.05,"Riktig.",IF(ABS(C37-(ROUND(C12/C14*100,1)))&lt;=0.05,"Du har glemt at totalkapitalen øker med lånet. Legg 1 190 000 til totalkapitalen før du deler.",IF(ABS(C37-(ROUND((C12-C15*C16/100)/C14*100,1)))&lt;=0.05,"Du har trukket lånet fra egenkapitalen. Et lån øker gjelden og totalkapitalen; egenkapitalen er den samme.","Ikke riktig ennå. 2 892 650 delt på (10 182 650 + 1 190 000), ganger 100."))))</f>
+        <f aca="false">IF(C37="","Skriv svaret i den gule cellen.",IF(ABS(C37-(ROUND(C12/(C14+C15*C16)*100,1)))&lt;=0.05,"Riktig.",IF(ABS(C37-(ROUND(C12/C14*100,1)))&lt;=0.05,"Du har glemt at totalkapitalen øker med lånet. Legg 990 000 til totalkapitalen før du deler.",IF(ABS(C37-(ROUND((C12-C15*C16)/C14*100,1)))&lt;=0.05,"Du har trukket lånet fra egenkapitalen. Et lån øker gjelden og totalkapitalen; egenkapitalen er den samme.","Ikke riktig ennå. 2 892 650 delt på (10 182 650 + 990 000), ganger 100."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
         <v>78</v>
       </c>
       <c r="G38" s="17" t="str">
-        <f aca="false">IF(C38="","Skriv svaret i den gule cellen.",IF(ABS(C38-(ROUND(C14*0.35-C12,0)))&lt;=1,"Riktig.",IF(ABS(C38-(ROUND(C14*0.35,0)))&lt;=1,"Det er egenkapitalen Nordlys måtte hatt. Trekk fra den egenkapitalen de har, 2 892 650.",IF(ABS(C38-(ROUND((C14+C15*C16/100)*0.35-C12,0)))&lt;=1,"Du har brukt totalkapitalen med lånet. Oppgaven spør om dagens balanse, 10 182 650.","Ikke riktig ennå. 35 % av 10 182 650 minus 2 892 650."))))</f>
+        <f aca="false">IF(C38="","Skriv svaret i den gule cellen.",IF(ABS(C38-(ROUND(C14*0.35-C12,0)))&lt;=1,"Riktig.",IF(ABS(C38-(ROUND(C14*0.35,0)))&lt;=1,"Det er egenkapitalen Nordlys måtte hatt. Trekk fra den egenkapitalen de har, 2 892 650.",IF(ABS(C38-(ROUND((C14+C15*C16)*0.35-C12,0)))&lt;=1,"Du har brukt totalkapitalen med lånet. Oppgaven spør om dagens balanse, 10 182 650.","Ikke riktig ennå. 35 % av 10 182 650 minus 2 892 650."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
     </row>
     <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="21" t="str">
-        <f aca="false">IF(LEN(B41)&lt;40,"",IF(AND(ISNUMBER(SEARCH("leder",B41)),ISNUMBER(SEARCH("egenkapital",B41))),"Bra: du tar både strukturen (en leder for solcelle og lading) og økonomien (egenkapitalen). Si også hva som er alternativet: forskudd fra borettslaget, eller å la mer av overskuddet bli stående.",IF(OR(ISNUMBER(SEARCH("leder",B41)),ISNUMBER(SEARCH("egenkapital",B41))),"Du har med ett av de to. Ta med det andre også: avdelingen trenger en leder som kan være prosjektleder, og egenkapitalandelen på 28,4 % er grunnen til at banken sier nei.","Tips: struktur: gi solcelle og lading en leder som kan lede ladejobben, og skriv ned hvem som bestemmer hva. Økonomi: med 71,6 % gjeld er Nordlys allerede over bokas grense på 60–65 %, og med lånt materiell faller egenkapitalandelen til 25,4 %. Be borettslaget om forskudd på materiellet, eller la mer av overskuddet bli stående til egenkapitalen er 671 278 kr høyere.")))</f>
+        <f aca="false">IF(LEN(B41)&lt;40,"",IF(AND(ISNUMBER(SEARCH("leder",B41)),ISNUMBER(SEARCH("egenkapital",B41))),"Bra: du tar både strukturen (en leder for solcelle og lading) og økonomien (egenkapitalen). Si også hva som er alternativet: forskudd fra borettslaget, eller å la mer av overskuddet bli stående.",IF(OR(ISNUMBER(SEARCH("leder",B41)),ISNUMBER(SEARCH("egenkapital",B41))),"Du har med ett av de to. Ta med det andre også: avdelingen trenger en leder som kan være prosjektleder, og egenkapitalandelen på 28,4 % er grunnen til at banken ikke vil stille garantien.","Tips: struktur: gi solcelle og lading en leder som kan lede ladejobben, og skriv ned hvem som bestemmer hva. Økonomi: med 71,6 % gjeld er Nordlys allerede over bokas grense på 60–65 %, og med lånt materiell faller egenkapitalandelen til 25,9 %. Avtal betalingsplan med a konto for materiellet i kontrakten, eller la mer av overskuddet bli stående til egenkapitalen er 671 278 kr høyere.")))</f>
         <v/>
       </c>
       <c r="C44" s="21"/>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="46" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="23" t="str">
-        <f aca="false">IF(C45="JA","Hint: a: det som står på papir er formelt; kommunikasjon, tillit, stemning og vaner er uformelt. b: subkultur. c: 2 892 650 / 10 182 650 × 100 = 28,4 %. d: 100 − 28,4 = 71,6 %. e: 35 % av 3 400 000 = 1 190 000 kr. f: 2 892 650 / 11 372 650 × 100 = 25,4 %. g: 35 % av 10 182 650 = 3 563 928, minus 2 892 650 = 671 278 kr.","")</f>
+        <f aca="false">IF(C45="JA","Hint: a: det som står på papir er formelt; kommunikasjon, tillit, stemning og vaner er uformelt. b: subkultur. c: 2 892 650 / 10 182 650 × 100 = 28,4 %. d: 100 − 28,4 = 71,6 %. e: 90 × 11 000 = 990 000 kr. f: 2 892 650 / 11 172 650 × 100 = 25,9 %. g: 35 % av 10 182 650 = 3 563 928, minus 2 892 650 = 671 278 kr.","")</f>
         <v/>
       </c>
       <c r="C46" s="23"/>
@@ -3198,7 +3198,7 @@
         <v>155</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>1190000</v>
+        <v>990000</v>
       </c>
       <c r="D22" s="28" t="s">
         <v>156</v>

--- a/pensum/ol12/OL12_Interne_rammebetingelser_Oppgaver_v6.xlsx
+++ b/pensum/ol12/OL12_Interne_rammebetingelser_Oppgaver_v6.xlsx
@@ -708,7 +708,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -823,6 +823,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1110,7 +1114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1135,27 +1139,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1317,8 +1321,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="29" r="B12" t="s">
         <v>26</v>
       </c>
       <c r="C12" s="13" t="n">
@@ -1339,8 +1343,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="29" r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="13" t="n">
@@ -1368,7 +1372,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="75.75" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="s">
         <v>30</v>
       </c>
@@ -1386,7 +1390,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="14" t="s">
         <v>31</v>
       </c>
@@ -1477,7 +1481,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="27" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="15" t="s">
         <v>45</v>
       </c>
@@ -1500,7 +1504,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="31" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="15" t="s">
         <v>48</v>
       </c>
@@ -1953,7 +1957,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="21" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="14" t="s">
         <v>65</v>
       </c>
@@ -2084,7 +2088,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="34" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="15" t="s">
         <v>80</v>
       </c>
@@ -2459,7 +2463,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
         <v>89</v>
       </c>
@@ -2568,7 +2572,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="90" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="9" t="s">
         <v>100</v>
       </c>
@@ -2578,7 +2582,7 @@
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="14" t="s">
         <v>101</v>
       </c>
@@ -2668,7 +2672,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="32" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="15" t="s">
         <v>110</v>
       </c>
@@ -2704,7 +2708,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="36" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="15" t="s">
         <v>114</v>
       </c>
@@ -2717,7 +2721,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="37" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="15" t="s">
         <v>115</v>
       </c>
@@ -2730,7 +2734,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="38" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="15" t="s">
         <v>116</v>
       </c>

--- a/pensum/ol12/OL12_Interne_rammebetingelser_Oppgaver_v6.xlsx
+++ b/pensum/ol12/OL12_Interne_rammebetingelser_Oppgaver_v6.xlsx
@@ -708,7 +708,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -823,10 +823,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1114,7 +1110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1139,27 +1135,27 @@
         <v>6</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1321,8 +1317,8 @@
         <v>15</v>
       </c>
     </row>
-    <row ht="31.5" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c s="29" r="B12" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="12" t="s">
         <v>26</v>
       </c>
       <c r="C12" s="13" t="n">
@@ -1343,8 +1339,8 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="31.5" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c s="29" r="B14" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="12" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="13" t="n">
@@ -1372,7 +1368,7 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="75.75" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="s">
         <v>30</v>
       </c>
@@ -1390,7 +1386,7 @@
         <v>17</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="14" t="s">
         <v>31</v>
       </c>
@@ -1481,7 +1477,7 @@
         <v>44</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="27" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="15" t="s">
         <v>45</v>
       </c>
@@ -1504,7 +1500,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="31" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="15" t="s">
         <v>48</v>
       </c>
@@ -1957,7 +1953,7 @@
         <v>54</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="21" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="14" t="s">
         <v>65</v>
       </c>
@@ -2088,7 +2084,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="34" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="15" t="s">
         <v>80</v>
       </c>
@@ -2463,7 +2459,7 @@
         <v>84</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
         <v>89</v>
       </c>
@@ -2572,7 +2568,7 @@
         <v>99</v>
       </c>
     </row>
-    <row ht="90" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="9" t="s">
         <v>100</v>
       </c>
@@ -2582,7 +2578,7 @@
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
     </row>
-    <row ht="17.25" customHeight="true" r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="14" t="s">
         <v>101</v>
       </c>
@@ -2672,7 +2668,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="32" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="15" t="s">
         <v>110</v>
       </c>
@@ -2708,7 +2704,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="36" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="15" t="s">
         <v>114</v>
       </c>
@@ -2721,7 +2717,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="37" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="15" t="s">
         <v>115</v>
       </c>
@@ -2734,7 +2730,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="38" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="15" t="s">
         <v>116</v>
       </c>
@@ -3213,7 +3209,7 @@
         <v>157</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="D23" s="28" t="s">
         <v>158</v>
